--- a/.work/export-template.xlsx
+++ b/.work/export-template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="送样记录" sheetId="1" r:id="R46c8bde3b4fa4795"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="归还明细" sheetId="2" r:id="Rbcac4a04fb3b4e52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="送样记录" sheetId="1" r:id="R3731ac5ffd07433b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="归还明细" sheetId="2" r:id="R40f78b9e4b8e457a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -594,6 +594,8 @@
     <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -608,6 +610,8 @@
       <x:c r="G1" s="3"/>
       <x:c r="H1" s="3"/>
       <x:c r="I1" s="3"/>
+      <x:c r="J1" s="3"/>
+      <x:c r="K1" s="3"/>
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="1" t="str">
@@ -621,6 +625,8 @@
       <x:c r="G2" s="1"/>
       <x:c r="H2" s="1"/>
       <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+      <x:c r="K2" s="1"/>
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="1"/>
@@ -632,6 +638,8 @@
       <x:c r="G3" s="1"/>
       <x:c r="H3" s="1"/>
       <x:c r="I3" s="1"/>
+      <x:c r="J3" s="1"/>
+      <x:c r="K3" s="1"/>
     </x:row>
     <x:row r="4" ht="28" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -661,6 +669,12 @@
       <x:c r="I4" s="6" t="str">
         <x:v>归还备注</x:v>
       </x:c>
+      <x:c r="J4" s="6" t="str">
+        <x:v>客户是否提供测试报告</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="str">
+        <x:v>测试报告文件名</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="28" customHeight="1">
       <x:c r="A5" s="8" t="str">
@@ -688,6 +702,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="8" t="str">
+        <x:v>示例</x:v>
+      </x:c>
+      <x:c r="J5" s="8" t="str">
+        <x:v>示例</x:v>
+      </x:c>
+      <x:c r="K5" s="8" t="str">
         <x:v>示例</x:v>
       </x:c>
     </x:row>
